--- a/האיש הנכון .xlsx
+++ b/האיש הנכון .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruthie Lax\פיתוח\האיש הנכון\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1B5C44-833A-4DA5-AF1C-CD4528B8C8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84C6E1A-9E2D-449C-83DF-EAE0AC6A273B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="מטפלים ופסיכיאטריים" sheetId="1" r:id="rId1"/>
@@ -354,7 +354,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.44140625" customWidth="1"/>
@@ -414,17 +414,31 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1">
+        <v>547353235</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
@@ -439,39 +453,16 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1">
-        <v>547353235</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
